--- a/product-definitions/spreadsheet/surface-met.xlsx
+++ b/product-definitions/spreadsheet/surface-met.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="103">
   <si>
     <t>Name</t>
   </si>
@@ -167,6 +167,12 @@
     <t>Hail Rate</t>
   </si>
   <si>
+    <t>surface_temperature</t>
+  </si>
+  <si>
+    <t>Surface Temperature</t>
+  </si>
+  <si>
     <t>downwelling_longwave_flux_in_air</t>
   </si>
   <si>
@@ -186,6 +192,36 @@
   </si>
   <si>
     <t>Downwelling Total Radiative Flux</t>
+  </si>
+  <si>
+    <t>direct_downwelling_shortwave_flux_in_air</t>
+  </si>
+  <si>
+    <t>Direct Downwelling Shortwave Radiation</t>
+  </si>
+  <si>
+    <t>diffuse_downwelling_shortwave_flux_in_air</t>
+  </si>
+  <si>
+    <t>Diffuse Downwelling Shortwave Radiation</t>
+  </si>
+  <si>
+    <t>upwelling_longwave_flux_in_air</t>
+  </si>
+  <si>
+    <t>Upwelling Longwave Radiation</t>
+  </si>
+  <si>
+    <t>upwelling_shortwave_flux_in_air</t>
+  </si>
+  <si>
+    <t>Upwelling Shortwave Radiation</t>
+  </si>
+  <si>
+    <t>upwelling_total_irradiance</t>
+  </si>
+  <si>
+    <t>Upwelling Total Radiative Flux</t>
   </si>
   <si>
     <t>net_total_irradiance</t>
@@ -316,7 +352,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -342,14 +378,9 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -377,7 +408,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -392,34 +423,42 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1720,7 +1759,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -1728,23 +1767,23 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -1752,7 +1791,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="5" t="s">
@@ -1760,52 +1799,52 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="5" t="s">
@@ -1813,31 +1852,31 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="5" t="s">
@@ -1845,1587 +1884,2061 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="6" t="s">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="B21" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="6" t="s">
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="B22" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="6" t="s">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="B23" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="6" t="s">
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="B24" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="s">
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="6" t="s">
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="6" t="s">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="B28" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="6" t="s">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="B29" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="6" t="s">
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="B30" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="6" t="s">
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="B31" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="6" t="s">
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="B32" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="6" t="s">
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="B33" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="6" t="s">
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="B34" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="6" t="s">
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="B35" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="6" t="s">
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="B36" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="6" t="s">
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="6" t="s">
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="6" t="s">
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="B40" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="6" t="s">
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="B41" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="6" t="s">
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="B42" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="6" t="s">
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="B43" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="6" t="s">
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="B44" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="6" t="s">
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="B45" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="6" t="s">
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="B46" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="6" t="s">
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="B47" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="6" t="s">
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="B48" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="6" t="s">
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="6" t="s">
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="B51" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="6" t="s">
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="B52" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="6" t="s">
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="6" t="s">
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="B54" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="6" t="s">
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="B55" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" s="6" t="s">
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="B56" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C56" s="7">
+      <c r="C56" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" s="6" t="s">
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="B57" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="6" t="s">
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="B58" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C58" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="6" t="s">
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="B59" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="6" t="s">
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="B60" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="6" t="s">
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="6" t="s">
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="B63" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="6" t="s">
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="B64" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="6" t="s">
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="B65" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C65" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" s="6" t="s">
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="B66" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" s="6" t="s">
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="B67" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="68">
-      <c r="B68" s="6" t="s">
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="B68" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C68" s="7">
+      <c r="C68" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" s="6" t="s">
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="B69" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="C69" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="70">
-      <c r="B70" s="6" t="s">
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="B70" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C70" s="8" t="s">
+      <c r="C70" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" s="6" t="s">
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="B71" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C71" s="6" t="s">
+      <c r="C71" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" s="6" t="s">
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="B72" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C72" s="6" t="s">
+      <c r="C72" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="6" t="s">
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="75">
-      <c r="B75" s="6" t="s">
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="B75" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" s="6" t="s">
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="B76" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C76" s="6" t="s">
+      <c r="C76" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" s="6" t="s">
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="B77" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C77" s="6" t="s">
+      <c r="C77" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="78">
-      <c r="B78" s="6" t="s">
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="B78" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C78" s="6" t="s">
+      <c r="C78" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="79">
-      <c r="B79" s="6" t="s">
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="B79" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C79" s="6" t="s">
+      <c r="C79" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="80">
-      <c r="B80" s="6" t="s">
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="B80" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C80" s="7">
+      <c r="C80" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="81">
-      <c r="B81" s="6" t="s">
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="B81" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C81" s="8" t="s">
+      <c r="C81" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="82">
-      <c r="B82" s="6" t="s">
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="B82" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C82" s="8" t="s">
+      <c r="C82" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="83">
-      <c r="B83" s="6" t="s">
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="B83" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C83" s="6" t="s">
+      <c r="C83" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="84">
-      <c r="B84" s="6" t="s">
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="B84" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C84" s="6" t="s">
+      <c r="C84" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="86">
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" s="6" t="s">
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="B87" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" s="6" t="s">
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="B88" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C88" s="6" t="s">
+      <c r="C88" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="89">
-      <c r="B89" s="6" t="s">
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="B89" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="90">
-      <c r="B90" s="6" t="s">
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="B90" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E90" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="91">
-      <c r="B91" s="6" t="s">
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="B91" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="92">
-      <c r="B92" s="6" t="s">
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="B92" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C92" s="7">
+      <c r="C92" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="93">
-      <c r="B93" s="6" t="s">
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="B93" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C93" s="8" t="s">
+      <c r="C93" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="94">
-      <c r="B94" s="6" t="s">
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="B94" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C94" s="8" t="s">
+      <c r="C94" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="95">
-      <c r="B95" s="6" t="s">
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="B95" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C95" s="6" t="s">
+      <c r="C95" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="96">
-      <c r="B96" s="6" t="s">
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="B96" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C96" s="6" t="s">
+      <c r="C96" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="98">
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="99">
-      <c r="B99" s="6" t="s">
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="B99" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="100">
-      <c r="B100" s="6" t="s">
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="B100" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C100" s="6" t="s">
+      <c r="C100" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="101">
-      <c r="B101" s="6" t="s">
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="B101" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="102">
-      <c r="B102" s="6" t="s">
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="B102" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E102" s="9" t="s">
+      <c r="E102" s="8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="103">
-      <c r="B103" s="6" t="s">
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="B103" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E103" s="9"/>
-    </row>
-    <row r="104">
-      <c r="B104" s="6" t="s">
+      <c r="E103" s="8"/>
+    </row>
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="B104" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C104" s="7">
+      <c r="C104" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="105">
-      <c r="B105" s="6" t="s">
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="B105" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C105" s="8" t="s">
+      <c r="C105" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="106">
-      <c r="B106" s="6" t="s">
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="B106" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C106" s="8" t="s">
+      <c r="C106" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="107">
-      <c r="B107" s="6" t="s">
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="B107" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C107" s="6" t="s">
+      <c r="C107" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="108">
-      <c r="B108" s="6" t="s">
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="B108" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C108" s="6" t="s">
+      <c r="C108" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="6" t="s">
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="A110" s="9" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="111">
-      <c r="B111" s="6" t="s">
+      <c r="B110" s="10"/>
+      <c r="C110" s="10"/>
+    </row>
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="A111" s="10"/>
+      <c r="B111" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C111" s="5" t="s">
+      <c r="C111" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="112">
-      <c r="B112" s="6" t="s">
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="A112" s="10"/>
+      <c r="B112" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C112" s="6" t="s">
+      <c r="C112" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="113">
-      <c r="B113" s="6" t="s">
+    <row r="113" ht="15.75" customHeight="1">
+      <c r="A113" s="10"/>
+      <c r="B113" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C113" s="6" t="s">
+      <c r="C113" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="A114" s="10"/>
+      <c r="B114" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C114" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="A115" s="10"/>
+      <c r="B115" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" s="9" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="114">
-      <c r="B114" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C114" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="B115" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" s="5" t="s">
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="A116" s="10"/>
+      <c r="B116" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C116" s="11">
+        <v>-1.0E20</v>
+      </c>
+    </row>
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="A117" s="10"/>
+      <c r="B117" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="118" ht="15.75" customHeight="1">
+      <c r="A118" s="10"/>
+      <c r="B118" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C118" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="A119" s="10"/>
+      <c r="B119" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C119" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="120" ht="15.75" customHeight="1">
+      <c r="A120" s="10"/>
+      <c r="B120" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C120" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1">
+      <c r="A122" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="116">
-      <c r="B116" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C116" s="7">
-        <v>-1.0E20</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="B117" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C117" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="B118" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C118" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="B119" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="B120" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C120" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="B123" s="6" t="s">
+    <row r="123" ht="15.75" customHeight="1">
+      <c r="B123" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C123" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="124">
-      <c r="B124" s="6" t="s">
+    <row r="124" ht="15.75" customHeight="1">
+      <c r="B124" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C124" s="6" t="s">
+      <c r="C124" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="125">
-      <c r="B125" s="6" t="s">
+    <row r="125" ht="15.75" customHeight="1">
+      <c r="B125" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C125" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="B126" s="6" t="s">
+      <c r="C125" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="126" ht="15.75" customHeight="1">
+      <c r="B126" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C126" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="B127" s="6" t="s">
+      <c r="C126" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="127" ht="15.75" customHeight="1">
+      <c r="B127" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="128">
-      <c r="B128" s="6" t="s">
+    <row r="128" ht="15.75" customHeight="1">
+      <c r="B128" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C128" s="7">
+      <c r="C128" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="129">
-      <c r="B129" s="6" t="s">
+    <row r="129" ht="15.75" customHeight="1">
+      <c r="B129" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C129" s="8" t="s">
+      <c r="C129" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="130">
-      <c r="B130" s="6" t="s">
+    <row r="130" ht="15.75" customHeight="1">
+      <c r="B130" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C130" s="8" t="s">
+      <c r="C130" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="131">
-      <c r="B131" s="6" t="s">
+    <row r="131" ht="15.75" customHeight="1">
+      <c r="B131" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C131" s="6" t="s">
+      <c r="C131" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="132">
-      <c r="B132" s="6" t="s">
+    <row r="132" ht="15.75" customHeight="1">
+      <c r="B132" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C132" s="6" t="s">
+      <c r="C132" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="5"/>
-    </row>
-    <row r="134">
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="135">
-      <c r="B135" s="6" t="s">
+    <row r="135" ht="15.75" customHeight="1">
+      <c r="B135" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C135" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="136">
-      <c r="B136" s="6" t="s">
+    <row r="136" ht="15.75" customHeight="1">
+      <c r="B136" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C136" s="6" t="s">
+      <c r="C136" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="137">
-      <c r="B137" s="6" t="s">
+    <row r="137" ht="15.75" customHeight="1">
+      <c r="B137" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C137" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="B138" s="6" t="s">
+      <c r="C137" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="138" ht="15.75" customHeight="1">
+      <c r="B138" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E138" s="10" t="s">
+      <c r="C138" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="139">
-      <c r="B139" s="6" t="s">
+    <row r="139" ht="15.75" customHeight="1">
+      <c r="B139" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C139" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="140">
-      <c r="B140" s="6" t="s">
+    <row r="140" ht="15.75" customHeight="1">
+      <c r="B140" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C140" s="7">
+      <c r="C140" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="141">
-      <c r="B141" s="6" t="s">
+    <row r="141" ht="15.75" customHeight="1">
+      <c r="B141" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C141" s="8" t="s">
+      <c r="C141" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="142">
-      <c r="B142" s="6" t="s">
+    <row r="142" ht="15.75" customHeight="1">
+      <c r="B142" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C142" s="8" t="s">
+      <c r="C142" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="143">
-      <c r="B143" s="6" t="s">
+    <row r="143" ht="15.75" customHeight="1">
+      <c r="B143" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C143" s="6" t="s">
+      <c r="C143" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="144">
-      <c r="B144" s="6" t="s">
+    <row r="144" ht="15.75" customHeight="1">
+      <c r="B144" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C144" s="6" t="s">
+      <c r="C144" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="146">
+    <row r="145" ht="15.75" customHeight="1">
+      <c r="A145" s="5"/>
+    </row>
+    <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="147">
-      <c r="B147" s="6" t="s">
+    <row r="147" ht="15.75" customHeight="1">
+      <c r="B147" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C147" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="148">
-      <c r="B148" s="6" t="s">
+    <row r="148" ht="15.75" customHeight="1">
+      <c r="B148" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C148" s="6" t="s">
+      <c r="C148" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="149">
-      <c r="B149" s="6" t="s">
+    <row r="149" ht="15.75" customHeight="1">
+      <c r="B149" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C149" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="B150" s="6" t="s">
+      <c r="C149" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="150" ht="15.75" customHeight="1">
+      <c r="B150" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E150" s="5" t="s">
+      <c r="E150" s="13" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="151">
-      <c r="B151" s="6" t="s">
+    <row r="151" ht="15.75" customHeight="1">
+      <c r="B151" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C151" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="152">
-      <c r="B152" s="6" t="s">
+    <row r="152" ht="15.75" customHeight="1">
+      <c r="B152" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C152" s="7">
+      <c r="C152" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="153">
-      <c r="B153" s="6" t="s">
+    <row r="153" ht="15.75" customHeight="1">
+      <c r="B153" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C153" s="8" t="s">
+      <c r="C153" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="154">
-      <c r="B154" s="6" t="s">
+    <row r="154" ht="15.75" customHeight="1">
+      <c r="B154" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C154" s="8" t="s">
+      <c r="C154" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="155">
-      <c r="B155" s="6" t="s">
+    <row r="155" ht="15.75" customHeight="1">
+      <c r="B155" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C155" s="6" t="s">
+      <c r="C155" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="156">
-      <c r="B156" s="6" t="s">
+    <row r="156" ht="15.75" customHeight="1">
+      <c r="B156" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C156" s="6" t="s">
+      <c r="C156" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="6" t="s">
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1">
+      <c r="A158" s="14" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="159">
-      <c r="B159" s="6" t="s">
+    <row r="159" ht="15.75" customHeight="1">
+      <c r="B159" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C159" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="160" ht="15.75" customHeight="1">
+      <c r="B160" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="161" ht="15.75" customHeight="1">
+      <c r="B161" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="162" ht="15.75" customHeight="1">
+      <c r="B162" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C162" s="14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="163" ht="15.75" customHeight="1">
+      <c r="B163" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" s="14" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="160">
-      <c r="B160" s="6" t="s">
+    <row r="164" ht="15.75" customHeight="1">
+      <c r="B164" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C164" s="6">
+        <v>-1.0E20</v>
+      </c>
+    </row>
+    <row r="165" ht="15.75" customHeight="1">
+      <c r="B165" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C165" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="166" ht="15.75" customHeight="1">
+      <c r="B166" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C166" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="167" ht="15.75" customHeight="1">
+      <c r="B167" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="168" ht="15.75" customHeight="1">
+      <c r="B168" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1">
+      <c r="A170" s="14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="171" ht="15.75" customHeight="1">
+      <c r="B171" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="172" ht="15.75" customHeight="1">
+      <c r="B172" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C160" s="6" t="s">
+      <c r="C172" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="161">
-      <c r="B161" s="6" t="s">
+    <row r="173" ht="15.75" customHeight="1">
+      <c r="B173" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C161" s="11">
+      <c r="C173" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="174" ht="15.75" customHeight="1">
+      <c r="B174" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C174" s="14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="175" ht="15.75" customHeight="1">
+      <c r="B175" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" s="14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="176" ht="15.75" customHeight="1">
+      <c r="B176" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C176" s="6">
+        <v>-1.0E20</v>
+      </c>
+    </row>
+    <row r="177" ht="15.75" customHeight="1">
+      <c r="B177" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C177" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="178" ht="15.75" customHeight="1">
+      <c r="B178" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C178" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="179" ht="15.75" customHeight="1">
+      <c r="B179" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="180" ht="15.75" customHeight="1">
+      <c r="B180" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1">
+      <c r="A182" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="183" ht="15.75" customHeight="1">
+      <c r="B183" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="184" ht="15.75" customHeight="1">
+      <c r="B184" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="185" ht="15.75" customHeight="1">
+      <c r="B185" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="186" ht="15.75" customHeight="1">
+      <c r="B186" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C186" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="187" ht="15.75" customHeight="1">
+      <c r="B187" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" s="14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="188" ht="15.75" customHeight="1">
+      <c r="B188" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C188" s="6">
+        <v>-1.0E20</v>
+      </c>
+    </row>
+    <row r="189" ht="15.75" customHeight="1">
+      <c r="B189" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C189" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="190" ht="15.75" customHeight="1">
+      <c r="B190" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="191" ht="15.75" customHeight="1">
+      <c r="B191" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="192" ht="15.75" customHeight="1">
+      <c r="B192" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1">
+      <c r="A194" s="14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="195" ht="15.75" customHeight="1">
+      <c r="B195" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="196" ht="15.75" customHeight="1">
+      <c r="B196" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="197" ht="15.75" customHeight="1">
+      <c r="B197" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="198" ht="15.75" customHeight="1">
+      <c r="B198" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C198" s="14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="199" ht="15.75" customHeight="1">
+      <c r="B199" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" s="14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="200" ht="15.75" customHeight="1">
+      <c r="B200" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C200" s="6">
+        <v>-1.0E20</v>
+      </c>
+    </row>
+    <row r="201" ht="15.75" customHeight="1">
+      <c r="B201" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C201" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="202" ht="15.75" customHeight="1">
+      <c r="B202" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C202" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="203" ht="15.75" customHeight="1">
+      <c r="B203" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C203" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="204" ht="15.75" customHeight="1">
+      <c r="B204" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C204" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="205" ht="15.75" customHeight="1">
+      <c r="A205" s="5"/>
+    </row>
+    <row r="206" ht="15.75" customHeight="1">
+      <c r="A206" s="14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="207" ht="15.75" customHeight="1">
+      <c r="B207" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C207" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="208" ht="15.75" customHeight="1">
+      <c r="B208" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C208" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="209" ht="15.75" customHeight="1">
+      <c r="B209" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C209" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="210" ht="15.75" customHeight="1">
+      <c r="B210" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="211" ht="15.75" customHeight="1">
+      <c r="B211" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C211" s="14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="212" ht="15.75" customHeight="1">
+      <c r="B212" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C212" s="6">
+        <v>-1.0E20</v>
+      </c>
+    </row>
+    <row r="213" ht="15.75" customHeight="1">
+      <c r="B213" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C213" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="214" ht="15.75" customHeight="1">
+      <c r="B214" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C214" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="215" ht="15.75" customHeight="1">
+      <c r="B215" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C215" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="216" ht="15.75" customHeight="1">
+      <c r="B216" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C216" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1">
+      <c r="A218" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="219" ht="15.75" customHeight="1">
+      <c r="B219" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C219" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="220" ht="15.75" customHeight="1">
+      <c r="B220" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C220" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="221" ht="15.75" customHeight="1">
+      <c r="B221" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C221" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="222" ht="15.75" customHeight="1">
+      <c r="B222" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E222" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="223" ht="15.75" customHeight="1">
+      <c r="B223" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C223" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="224" ht="15.75" customHeight="1">
+      <c r="B224" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C224" s="6">
+        <v>-1.0E20</v>
+      </c>
+    </row>
+    <row r="225" ht="15.75" customHeight="1">
+      <c r="B225" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C225" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="226" ht="15.75" customHeight="1">
+      <c r="B226" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C226" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="227" ht="15.75" customHeight="1">
+      <c r="B227" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C227" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="228" ht="15.75" customHeight="1">
+      <c r="B228" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C228" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1">
+      <c r="A230" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="231" ht="15.75" customHeight="1">
+      <c r="B231" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C231" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="232" ht="15.75" customHeight="1">
+      <c r="B232" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C232" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="233" ht="15.75" customHeight="1">
+      <c r="B233" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C233" s="15">
         <v>1.0</v>
       </c>
     </row>
-    <row r="162">
-      <c r="B162" s="6" t="s">
+    <row r="234" ht="15.75" customHeight="1">
+      <c r="B234" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C162" s="11"/>
-    </row>
-    <row r="163">
-      <c r="B163" s="6" t="s">
+      <c r="C234" s="15"/>
+    </row>
+    <row r="235" ht="15.75" customHeight="1">
+      <c r="B235" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C163" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="B164" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C164" s="12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="B165" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C165" s="14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="B168" s="6" t="s">
+      <c r="C235" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="236" ht="15.75" customHeight="1">
+      <c r="B236" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C236" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="237" ht="15.75" customHeight="1">
+      <c r="B237" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C237" s="18" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1">
+      <c r="A239" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="240" ht="15.75" customHeight="1">
+      <c r="B240" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C168" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="B169" s="6" t="s">
+      <c r="C240" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="241" ht="15.75" customHeight="1">
+      <c r="B241" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C169" s="6" t="s">
+      <c r="C241" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="170">
-      <c r="B170" s="6" t="s">
+    <row r="242" ht="15.75" customHeight="1">
+      <c r="B242" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C170" s="11">
+      <c r="C242" s="15">
         <v>1.0</v>
       </c>
     </row>
-    <row r="171">
-      <c r="B171" s="6" t="s">
+    <row r="243" ht="15.75" customHeight="1">
+      <c r="B243" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C171" s="11"/>
-    </row>
-    <row r="172">
-      <c r="B172" s="6" t="s">
+      <c r="C243" s="15"/>
+    </row>
+    <row r="244" ht="15.75" customHeight="1">
+      <c r="B244" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C172" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="B173" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C173" s="12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="B174" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C174" s="14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="B177" s="6" t="s">
+      <c r="C244" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="245" ht="15.75" customHeight="1">
+      <c r="B245" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C245" s="16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="246" ht="15.75" customHeight="1">
+      <c r="B246" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C246" s="18" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1">
+      <c r="A248" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="249" ht="15.75" customHeight="1">
+      <c r="B249" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C177" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="B178" s="6" t="s">
+      <c r="C249" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="250" ht="15.75" customHeight="1">
+      <c r="B250" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C178" s="6" t="s">
+      <c r="C250" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="179">
-      <c r="B179" s="6" t="s">
+    <row r="251" ht="15.75" customHeight="1">
+      <c r="B251" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C179" s="11">
+      <c r="C251" s="15">
         <v>1.0</v>
       </c>
     </row>
-    <row r="180">
-      <c r="B180" s="6" t="s">
+    <row r="252" ht="15.75" customHeight="1">
+      <c r="B252" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C180" s="11"/>
-    </row>
-    <row r="181">
-      <c r="B181" s="6" t="s">
+      <c r="C252" s="15"/>
+    </row>
+    <row r="253" ht="15.75" customHeight="1">
+      <c r="B253" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C181" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="B182" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C182" s="12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="B183" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C183" s="14" t="s">
+      <c r="C253" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="254" ht="15.75" customHeight="1">
+      <c r="B254" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C254" s="16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="255" ht="15.75" customHeight="1">
+      <c r="B255" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C255" s="18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1">
+      <c r="A257" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="258" ht="15.75" customHeight="1">
+      <c r="B258" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C258" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="B186" s="6" t="s">
+    <row r="259" ht="15.75" customHeight="1">
+      <c r="B259" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C259" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="260" ht="15.75" customHeight="1">
+      <c r="B260" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C260" s="15">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="261" ht="15.75" customHeight="1">
+      <c r="B261" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C261" s="15"/>
+    </row>
+    <row r="262" ht="15.75" customHeight="1">
+      <c r="B262" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C262" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="263" ht="15.75" customHeight="1">
+      <c r="B263" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C263" s="16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="264" ht="15.75" customHeight="1">
+      <c r="B264" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C264" s="18" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1">
+      <c r="A266" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="267" ht="15.75" customHeight="1">
+      <c r="B267" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C186" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="B187" s="6" t="s">
+      <c r="C267" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="268" ht="15.75" customHeight="1">
+      <c r="B268" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C187" s="6" t="s">
+      <c r="C268" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="188">
-      <c r="B188" s="6" t="s">
+    <row r="269" ht="15.75" customHeight="1">
+      <c r="B269" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C188" s="11">
+      <c r="C269" s="15">
         <v>1.0</v>
       </c>
     </row>
-    <row r="189">
-      <c r="B189" s="6" t="s">
+    <row r="270" ht="15.75" customHeight="1">
+      <c r="B270" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C189" s="11"/>
-    </row>
-    <row r="190">
-      <c r="B190" s="6" t="s">
+      <c r="C270" s="15"/>
+    </row>
+    <row r="271" ht="15.75" customHeight="1">
+      <c r="B271" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C190" s="5" t="s">
+      <c r="C271" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="272" ht="15.75" customHeight="1">
+      <c r="B272" s="8" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="191">
-      <c r="B191" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C191" s="12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="B192" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C192" s="15" t="s">
+      <c r="C272" s="16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="273" ht="15.75" customHeight="1">
+      <c r="B273" s="17" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="B195" s="6" t="s">
+      <c r="C273" s="18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1">
+      <c r="A275" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="276" ht="15.75" customHeight="1">
+      <c r="B276" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C195" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="B196" s="6" t="s">
+      <c r="C276" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="277" ht="15.75" customHeight="1">
+      <c r="B277" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C196" s="6" t="s">
+      <c r="C277" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="197">
-      <c r="B197" s="6" t="s">
+    <row r="278" ht="15.75" customHeight="1">
+      <c r="B278" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C197" s="11">
+      <c r="C278" s="15">
         <v>1.0</v>
       </c>
     </row>
-    <row r="198">
-      <c r="B198" s="6" t="s">
+    <row r="279" ht="15.75" customHeight="1">
+      <c r="B279" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C198" s="11"/>
-    </row>
-    <row r="199">
-      <c r="B199" s="6" t="s">
+      <c r="C279" s="15"/>
+    </row>
+    <row r="280" ht="15.75" customHeight="1">
+      <c r="B280" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C199" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="B200" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C200" s="16" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="B201" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C201" s="15" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="B204" s="6" t="s">
+      <c r="C280" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="281" ht="15.75" customHeight="1">
+      <c r="B281" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C281" s="16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="282" ht="15.75" customHeight="1">
+      <c r="B282" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C282" s="18" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1">
+      <c r="A284" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="285" ht="15.75" customHeight="1">
+      <c r="B285" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C204" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="B205" s="6" t="s">
+      <c r="C285" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="286" ht="15.75" customHeight="1">
+      <c r="B286" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C205" s="6" t="s">
+      <c r="C286" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="206">
-      <c r="B206" s="6" t="s">
+    <row r="287" ht="15.75" customHeight="1">
+      <c r="B287" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C206" s="11">
+      <c r="C287" s="15">
         <v>1.0</v>
       </c>
     </row>
-    <row r="207">
-      <c r="B207" s="6" t="s">
+    <row r="288" ht="15.75" customHeight="1">
+      <c r="B288" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C207" s="11"/>
-    </row>
-    <row r="208">
-      <c r="B208" s="6" t="s">
+      <c r="C288" s="15"/>
+    </row>
+    <row r="289" ht="15.75" customHeight="1">
+      <c r="B289" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C208" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="B209" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C209" s="12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="B210" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C210" s="14" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="B213" s="6" t="s">
+      <c r="C289" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="290" ht="15.75" customHeight="1">
+      <c r="B290" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C290" s="16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="291" ht="15.75" customHeight="1">
+      <c r="B291" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C291" s="18" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1">
+      <c r="A293" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="294" ht="15.75" customHeight="1">
+      <c r="B294" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C213" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="B214" s="6" t="s">
+      <c r="C294" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="295" ht="15.75" customHeight="1">
+      <c r="B295" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C214" s="6" t="s">
+      <c r="C295" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="215">
-      <c r="B215" s="6" t="s">
+    <row r="296" ht="15.75" customHeight="1">
+      <c r="B296" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C215" s="11">
+      <c r="C296" s="15">
         <v>1.0</v>
       </c>
     </row>
-    <row r="216">
-      <c r="B216" s="6" t="s">
+    <row r="297" ht="15.75" customHeight="1">
+      <c r="B297" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C216" s="11"/>
-    </row>
-    <row r="217">
-      <c r="B217" s="6" t="s">
+      <c r="C297" s="15"/>
+    </row>
+    <row r="298" ht="15.75" customHeight="1">
+      <c r="B298" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C217" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="B218" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C218" s="12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="B219" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C219" s="14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="B222" s="6" t="s">
+      <c r="C298" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="299" ht="15.75" customHeight="1">
+      <c r="B299" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C299" s="16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="300" ht="15.75" customHeight="1">
+      <c r="B300" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C300" s="18" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1">
+      <c r="A302" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="303" ht="15.75" customHeight="1">
+      <c r="B303" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C222" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="B223" s="6" t="s">
+      <c r="C303" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="304" ht="15.75" customHeight="1">
+      <c r="B304" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C223" s="6" t="s">
+      <c r="C304" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="224">
-      <c r="B224" s="6" t="s">
+    <row r="305" ht="15.75" customHeight="1">
+      <c r="B305" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C224" s="11">
+      <c r="C305" s="15">
         <v>1.0</v>
       </c>
     </row>
-    <row r="225">
-      <c r="B225" s="6" t="s">
+    <row r="306" ht="15.75" customHeight="1">
+      <c r="B306" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C225" s="11"/>
-    </row>
-    <row r="226">
-      <c r="B226" s="6" t="s">
+      <c r="C306" s="15"/>
+    </row>
+    <row r="307" ht="15.75" customHeight="1">
+      <c r="B307" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C226" s="5" t="s">
+      <c r="C307" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="308" ht="15.75" customHeight="1">
+      <c r="B308" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C308" s="16" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="227">
-      <c r="B227" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C227" s="12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="B228" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C228" s="14" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="B231" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C231" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="B232" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C232" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="B233" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C233" s="11">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="B234" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C234" s="11"/>
-    </row>
-    <row r="235">
-      <c r="B235" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C235" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="B236" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C236" s="12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="B237" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C237" s="14" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="238" ht="12.0" customHeight="1"/>
-    <row r="239" ht="12.0" customHeight="1"/>
-    <row r="240" ht="12.0" customHeight="1"/>
-    <row r="241" ht="12.0" customHeight="1"/>
-    <row r="242" ht="12.0" customHeight="1"/>
-    <row r="243" ht="12.0" customHeight="1"/>
-    <row r="244" ht="12.0" customHeight="1"/>
-    <row r="245" ht="12.0" customHeight="1"/>
-    <row r="246" ht="12.0" customHeight="1"/>
-    <row r="247" ht="12.0" customHeight="1"/>
-    <row r="248" ht="12.0" customHeight="1"/>
-    <row r="249" ht="12.0" customHeight="1"/>
-    <row r="250" ht="12.0" customHeight="1"/>
-    <row r="251" ht="12.0" customHeight="1"/>
-    <row r="252" ht="12.0" customHeight="1"/>
-    <row r="253" ht="12.0" customHeight="1"/>
-    <row r="254" ht="12.0" customHeight="1"/>
-    <row r="255" ht="12.0" customHeight="1"/>
-    <row r="256" ht="12.0" customHeight="1"/>
-    <row r="257" ht="12.0" customHeight="1"/>
-    <row r="258" ht="12.0" customHeight="1"/>
-    <row r="259" ht="12.0" customHeight="1"/>
-    <row r="260" ht="12.0" customHeight="1"/>
-    <row r="261" ht="12.0" customHeight="1"/>
-    <row r="262" ht="12.0" customHeight="1"/>
-    <row r="263" ht="12.0" customHeight="1"/>
-    <row r="264" ht="12.0" customHeight="1"/>
-    <row r="265" ht="12.0" customHeight="1"/>
-    <row r="266" ht="12.0" customHeight="1"/>
-    <row r="267" ht="12.0" customHeight="1"/>
-    <row r="268" ht="12.0" customHeight="1"/>
-    <row r="269" ht="12.0" customHeight="1"/>
-    <row r="270" ht="12.0" customHeight="1"/>
-    <row r="271" ht="12.0" customHeight="1"/>
-    <row r="272" ht="12.0" customHeight="1"/>
-    <row r="273" ht="12.0" customHeight="1"/>
-    <row r="274" ht="12.0" customHeight="1"/>
-    <row r="275" ht="12.0" customHeight="1"/>
-    <row r="276" ht="12.0" customHeight="1"/>
-    <row r="277" ht="12.0" customHeight="1"/>
-    <row r="278" ht="12.0" customHeight="1"/>
-    <row r="279" ht="12.0" customHeight="1"/>
-    <row r="280" ht="12.0" customHeight="1"/>
-    <row r="281" ht="12.0" customHeight="1"/>
-    <row r="282" ht="12.0" customHeight="1"/>
-    <row r="283" ht="12.0" customHeight="1"/>
-    <row r="284" ht="12.0" customHeight="1"/>
-    <row r="285" ht="12.0" customHeight="1"/>
-    <row r="286" ht="12.0" customHeight="1"/>
-    <row r="287" ht="12.0" customHeight="1"/>
-    <row r="288" ht="12.0" customHeight="1"/>
-    <row r="289" ht="12.0" customHeight="1"/>
-    <row r="290" ht="12.0" customHeight="1"/>
-    <row r="291" ht="12.0" customHeight="1"/>
-    <row r="292" ht="12.0" customHeight="1"/>
-    <row r="293" ht="12.0" customHeight="1"/>
-    <row r="294" ht="12.0" customHeight="1"/>
-    <row r="295" ht="12.0" customHeight="1"/>
-    <row r="296" ht="12.0" customHeight="1"/>
-    <row r="297" ht="12.0" customHeight="1"/>
-    <row r="298" ht="12.0" customHeight="1"/>
-    <row r="299" ht="12.0" customHeight="1"/>
-    <row r="300" ht="12.0" customHeight="1"/>
-    <row r="301" ht="12.0" customHeight="1"/>
-    <row r="302" ht="12.0" customHeight="1"/>
-    <row r="303" ht="12.0" customHeight="1"/>
-    <row r="304" ht="12.0" customHeight="1"/>
-    <row r="305" ht="12.0" customHeight="1"/>
-    <row r="306" ht="12.0" customHeight="1"/>
-    <row r="307" ht="12.0" customHeight="1"/>
-    <row r="308" ht="12.0" customHeight="1"/>
-    <row r="309" ht="12.0" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1">
+      <c r="B309" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C309" s="18" t="s">
+        <v>95</v>
+      </c>
+    </row>
     <row r="310" ht="12.0" customHeight="1"/>
     <row r="311" ht="12.0" customHeight="1"/>
     <row r="312" ht="12.0" customHeight="1"/>
@@ -3554,78 +4067,78 @@
     <row r="435" ht="12.0" customHeight="1"/>
     <row r="436" ht="12.0" customHeight="1"/>
     <row r="437" ht="12.0" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="438" ht="12.0" customHeight="1"/>
+    <row r="439" ht="12.0" customHeight="1"/>
+    <row r="440" ht="12.0" customHeight="1"/>
+    <row r="441" ht="12.0" customHeight="1"/>
+    <row r="442" ht="12.0" customHeight="1"/>
+    <row r="443" ht="12.0" customHeight="1"/>
+    <row r="444" ht="12.0" customHeight="1"/>
+    <row r="445" ht="12.0" customHeight="1"/>
+    <row r="446" ht="12.0" customHeight="1"/>
+    <row r="447" ht="12.0" customHeight="1"/>
+    <row r="448" ht="12.0" customHeight="1"/>
+    <row r="449" ht="12.0" customHeight="1"/>
+    <row r="450" ht="12.0" customHeight="1"/>
+    <row r="451" ht="12.0" customHeight="1"/>
+    <row r="452" ht="12.0" customHeight="1"/>
+    <row r="453" ht="12.0" customHeight="1"/>
+    <row r="454" ht="12.0" customHeight="1"/>
+    <row r="455" ht="12.0" customHeight="1"/>
+    <row r="456" ht="12.0" customHeight="1"/>
+    <row r="457" ht="12.0" customHeight="1"/>
+    <row r="458" ht="12.0" customHeight="1"/>
+    <row r="459" ht="12.0" customHeight="1"/>
+    <row r="460" ht="12.0" customHeight="1"/>
+    <row r="461" ht="12.0" customHeight="1"/>
+    <row r="462" ht="12.0" customHeight="1"/>
+    <row r="463" ht="12.0" customHeight="1"/>
+    <row r="464" ht="12.0" customHeight="1"/>
+    <row r="465" ht="12.0" customHeight="1"/>
+    <row r="466" ht="12.0" customHeight="1"/>
+    <row r="467" ht="12.0" customHeight="1"/>
+    <row r="468" ht="12.0" customHeight="1"/>
+    <row r="469" ht="12.0" customHeight="1"/>
+    <row r="470" ht="12.0" customHeight="1"/>
+    <row r="471" ht="12.0" customHeight="1"/>
+    <row r="472" ht="12.0" customHeight="1"/>
+    <row r="473" ht="12.0" customHeight="1"/>
+    <row r="474" ht="12.0" customHeight="1"/>
+    <row r="475" ht="12.0" customHeight="1"/>
+    <row r="476" ht="12.0" customHeight="1"/>
+    <row r="477" ht="12.0" customHeight="1"/>
+    <row r="478" ht="12.0" customHeight="1"/>
+    <row r="479" ht="12.0" customHeight="1"/>
+    <row r="480" ht="12.0" customHeight="1"/>
+    <row r="481" ht="12.0" customHeight="1"/>
+    <row r="482" ht="12.0" customHeight="1"/>
+    <row r="483" ht="12.0" customHeight="1"/>
+    <row r="484" ht="12.0" customHeight="1"/>
+    <row r="485" ht="12.0" customHeight="1"/>
+    <row r="486" ht="12.0" customHeight="1"/>
+    <row r="487" ht="12.0" customHeight="1"/>
+    <row r="488" ht="12.0" customHeight="1"/>
+    <row r="489" ht="12.0" customHeight="1"/>
+    <row r="490" ht="12.0" customHeight="1"/>
+    <row r="491" ht="12.0" customHeight="1"/>
+    <row r="492" ht="12.0" customHeight="1"/>
+    <row r="493" ht="12.0" customHeight="1"/>
+    <row r="494" ht="12.0" customHeight="1"/>
+    <row r="495" ht="12.0" customHeight="1"/>
+    <row r="496" ht="12.0" customHeight="1"/>
+    <row r="497" ht="12.0" customHeight="1"/>
+    <row r="498" ht="12.0" customHeight="1"/>
+    <row r="499" ht="12.0" customHeight="1"/>
+    <row r="500" ht="12.0" customHeight="1"/>
+    <row r="501" ht="12.0" customHeight="1"/>
+    <row r="502" ht="12.0" customHeight="1"/>
+    <row r="503" ht="12.0" customHeight="1"/>
+    <row r="504" ht="12.0" customHeight="1"/>
+    <row r="505" ht="12.0" customHeight="1"/>
+    <row r="506" ht="12.0" customHeight="1"/>
+    <row r="507" ht="12.0" customHeight="1"/>
+    <row r="508" ht="12.0" customHeight="1"/>
+    <row r="509" ht="12.0" customHeight="1"/>
     <row r="510" ht="15.75" customHeight="1"/>
     <row r="511" ht="15.75" customHeight="1"/>
     <row r="512" ht="15.75" customHeight="1"/>
@@ -4117,6 +4630,78 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
+    <row r="1006" ht="15.75" customHeight="1"/>
+    <row r="1007" ht="15.75" customHeight="1"/>
+    <row r="1008" ht="15.75" customHeight="1"/>
+    <row r="1009" ht="15.75" customHeight="1"/>
+    <row r="1010" ht="15.75" customHeight="1"/>
+    <row r="1011" ht="15.75" customHeight="1"/>
+    <row r="1012" ht="15.75" customHeight="1"/>
+    <row r="1013" ht="15.75" customHeight="1"/>
+    <row r="1014" ht="15.75" customHeight="1"/>
+    <row r="1015" ht="15.75" customHeight="1"/>
+    <row r="1016" ht="15.75" customHeight="1"/>
+    <row r="1017" ht="15.75" customHeight="1"/>
+    <row r="1018" ht="15.75" customHeight="1"/>
+    <row r="1019" ht="15.75" customHeight="1"/>
+    <row r="1020" ht="15.75" customHeight="1"/>
+    <row r="1021" ht="15.75" customHeight="1"/>
+    <row r="1022" ht="15.75" customHeight="1"/>
+    <row r="1023" ht="15.75" customHeight="1"/>
+    <row r="1024" ht="15.75" customHeight="1"/>
+    <row r="1025" ht="15.75" customHeight="1"/>
+    <row r="1026" ht="15.75" customHeight="1"/>
+    <row r="1027" ht="15.75" customHeight="1"/>
+    <row r="1028" ht="15.75" customHeight="1"/>
+    <row r="1029" ht="15.75" customHeight="1"/>
+    <row r="1030" ht="15.75" customHeight="1"/>
+    <row r="1031" ht="15.75" customHeight="1"/>
+    <row r="1032" ht="15.75" customHeight="1"/>
+    <row r="1033" ht="15.75" customHeight="1"/>
+    <row r="1034" ht="15.75" customHeight="1"/>
+    <row r="1035" ht="15.75" customHeight="1"/>
+    <row r="1036" ht="15.75" customHeight="1"/>
+    <row r="1037" ht="15.75" customHeight="1"/>
+    <row r="1038" ht="15.75" customHeight="1"/>
+    <row r="1039" ht="15.75" customHeight="1"/>
+    <row r="1040" ht="15.75" customHeight="1"/>
+    <row r="1041" ht="15.75" customHeight="1"/>
+    <row r="1042" ht="15.75" customHeight="1"/>
+    <row r="1043" ht="15.75" customHeight="1"/>
+    <row r="1044" ht="15.75" customHeight="1"/>
+    <row r="1045" ht="15.75" customHeight="1"/>
+    <row r="1046" ht="15.75" customHeight="1"/>
+    <row r="1047" ht="15.75" customHeight="1"/>
+    <row r="1048" ht="15.75" customHeight="1"/>
+    <row r="1049" ht="15.75" customHeight="1"/>
+    <row r="1050" ht="15.75" customHeight="1"/>
+    <row r="1051" ht="15.75" customHeight="1"/>
+    <row r="1052" ht="15.75" customHeight="1"/>
+    <row r="1053" ht="15.75" customHeight="1"/>
+    <row r="1054" ht="15.75" customHeight="1"/>
+    <row r="1055" ht="15.75" customHeight="1"/>
+    <row r="1056" ht="15.75" customHeight="1"/>
+    <row r="1057" ht="15.75" customHeight="1"/>
+    <row r="1058" ht="15.75" customHeight="1"/>
+    <row r="1059" ht="15.75" customHeight="1"/>
+    <row r="1060" ht="15.75" customHeight="1"/>
+    <row r="1061" ht="15.75" customHeight="1"/>
+    <row r="1062" ht="15.75" customHeight="1"/>
+    <row r="1063" ht="15.75" customHeight="1"/>
+    <row r="1064" ht="15.75" customHeight="1"/>
+    <row r="1065" ht="15.75" customHeight="1"/>
+    <row r="1066" ht="15.75" customHeight="1"/>
+    <row r="1067" ht="15.75" customHeight="1"/>
+    <row r="1068" ht="15.75" customHeight="1"/>
+    <row r="1069" ht="15.75" customHeight="1"/>
+    <row r="1070" ht="15.75" customHeight="1"/>
+    <row r="1071" ht="15.75" customHeight="1"/>
+    <row r="1072" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
